--- a/ig/improve-doc/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/improve-doc/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="572">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240329120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1735,6 +1735,9 @@
   </si>
   <si>
     <t>Urgences pédiatriques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R359-SurspecialiteTransversale/FHIR/TRE-R359-SurspecialiteTransversale</t>
   </si>
 </sst>
 </file>
@@ -2294,7 +2297,7 @@
         <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>518</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
